--- a/assets/database_structure/contact_list.xlsx
+++ b/assets/database_structure/contact_list.xlsx
@@ -32,7 +32,7 @@
     <t>contact_name</t>
   </si>
   <si>
-    <t>contact_phone</t>
+    <t>contact_mobile</t>
   </si>
   <si>
     <t>contact_email</t>

--- a/assets/database_structure/contact_list.xlsx
+++ b/assets/database_structure/contact_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28160" windowHeight="11400"/>
+    <workbookView windowWidth="28160" windowHeight="11240"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="18" r:id="rId1"/>
